--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_20-03-2026.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£46.64</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/celotex-xr4200-200mm-x-2-4m-x-1-2m-pallet-of-12</t>
+          <t>£935.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£51.2</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='onlineinsulation-sales.com', port=443): Read timed out. (read timeout=30)</t>
+          <t>£44.55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
+          <t>£42.95</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
